--- a/data/2FEB_25_26/clutch_aggregated_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_aggregated_25_26_2FEB.xlsx
@@ -2432,37 +2432,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>42.4</v>
+        <v>47.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2544</v>
+        <v>2832</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
         <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2471,28 +2471,28 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>32.4083466981132</v>
+        <v>31.69970127118643</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W27" t="n">
-        <v>12.05631367924528</v>
+        <v>12.75126483050847</v>
       </c>
     </row>
     <row r="28">
@@ -2507,37 +2507,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>35.55</v>
+        <v>40.35</v>
       </c>
       <c r="E28" t="n">
-        <v>2133</v>
+        <v>2421</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
         <v>5</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>14.08701265822785</v>
+        <v>14.9748029739777</v>
       </c>
       <c r="V28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W28" t="n">
-        <v>12.72382278481012</v>
+        <v>13.45734572490706</v>
       </c>
     </row>
     <row r="29">
@@ -2582,28 +2582,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>39.15</v>
+        <v>43.95</v>
       </c>
       <c r="E29" t="n">
-        <v>2349</v>
+        <v>2637</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -2636,13 +2636,13 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>12.81041890166028</v>
+        <v>14.30552673492605</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>7.832618135376752</v>
+        <v>9.040250284414103</v>
       </c>
     </row>
     <row r="30">
@@ -2732,25 +2732,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1.23</v>
+        <v>6.01</v>
       </c>
       <c r="E31" t="n">
-        <v>73.8</v>
+        <v>360.6</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2777,22 +2777,22 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7.022861896838601</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>-13.64</v>
+        <v>22.0708153078203</v>
       </c>
     </row>
     <row r="32">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>34.71</v>
+        <v>34.73</v>
       </c>
       <c r="E35" t="n">
-        <v>2082.6</v>
+        <v>2083.8</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>32.488965715932</v>
+        <v>32.47025626259718</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>12.98090463843273</v>
+        <v>12.97342931183415</v>
       </c>
     </row>
     <row r="36">
@@ -3257,22 +3257,22 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>44.77</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2686.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19</v>
+      </c>
+      <c r="H38" t="n">
         <v>11</v>
-      </c>
-      <c r="D38" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2398.2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>17</v>
-      </c>
-      <c r="H38" t="n">
-        <v>10</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>13</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3296,28 +3296,28 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U38" t="n">
-        <v>38.98470102576931</v>
+        <v>37.64615814161267</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>10.32533900425319</v>
+        <v>11.24359615814161</v>
       </c>
     </row>
     <row r="39">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>36.55</v>
+        <v>41.35</v>
       </c>
       <c r="E55" t="n">
-        <v>2193</v>
+        <v>2481</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4586,13 +4586,13 @@
         <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>25.12594801641587</v>
+        <v>23.36080773881499</v>
       </c>
       <c r="V55" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="W55" t="n">
-        <v>-11.16829001367989</v>
+        <v>-12.06464328899637</v>
       </c>
     </row>
     <row r="56">
@@ -4832,13 +4832,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" t="n">
-        <v>62.41</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>3744.6</v>
+        <v>4032.6</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4877,22 +4877,22 @@
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>8.590522352187149</v>
+        <v>7.977004909983632</v>
       </c>
       <c r="V59" t="n">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="W59" t="n">
-        <v>-15.53247876942798</v>
+        <v>-15.7722660318405</v>
       </c>
     </row>
     <row r="60">
@@ -4907,22 +4907,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60" t="n">
-        <v>57.63</v>
+        <v>62.43</v>
       </c>
       <c r="E60" t="n">
-        <v>3457.8</v>
+        <v>3745.8</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60" t="n">
         <v>4</v>
@@ -4931,13 +4931,13 @@
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L60" t="n">
         <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -4949,25 +4949,25 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U60" t="n">
-        <v>17.18349123720284</v>
+        <v>18.48644241550537</v>
       </c>
       <c r="V60" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="W60" t="n">
-        <v>2.277836196425476</v>
+        <v>0.650323562389879</v>
       </c>
     </row>
     <row r="61">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" t="n">
-        <v>35.64</v>
+        <v>35.74</v>
       </c>
       <c r="E61" t="n">
-        <v>2138.4</v>
+        <v>2144.4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>52.35871212121212</v>
+        <v>52.21221320649133</v>
       </c>
       <c r="V61" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="W61" t="n">
-        <v>21.98105780022446</v>
+        <v>21.63975657526581</v>
       </c>
     </row>
     <row r="62">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D63" t="n">
-        <v>30.7</v>
+        <v>35.4</v>
       </c>
       <c r="E63" t="n">
-        <v>1842</v>
+        <v>2124</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -5156,10 +5156,10 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
+        <v>13</v>
+      </c>
+      <c r="L63" t="n">
         <v>11</v>
-      </c>
-      <c r="L63" t="n">
-        <v>9</v>
       </c>
       <c r="M63" t="n">
         <v>0.5</v>
@@ -5186,13 +5186,13 @@
         <v>6</v>
       </c>
       <c r="U63" t="n">
-        <v>24.47924755700326</v>
+        <v>22.51570338983051</v>
       </c>
       <c r="V63" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="W63" t="n">
-        <v>-7.154648208469056</v>
+        <v>-4.591601694915255</v>
       </c>
     </row>
     <row r="64">
@@ -5282,37 +5282,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>57.05</v>
+        <v>61.85</v>
       </c>
       <c r="E65" t="n">
-        <v>3423</v>
+        <v>3711</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H65" t="n">
         <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L65" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4411764705882353</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -5321,10 +5321,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q65" t="n">
         <v>4</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
       </c>
       <c r="R65" t="n">
         <v>7</v>
@@ -5336,13 +5336,13 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>31.72787204206837</v>
+        <v>33.70003395311237</v>
       </c>
       <c r="V65" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="W65" t="n">
-        <v>4.324916739702013</v>
+        <v>2.523274050121261</v>
       </c>
     </row>
     <row r="66">
@@ -7382,22 +7382,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>11.32</v>
+        <v>12.84</v>
       </c>
       <c r="E93" t="n">
-        <v>679.2</v>
+        <v>770.4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
         <v>3</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -7436,13 +7436,13 @@
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>42.96235865724381</v>
+        <v>41.82207943925233</v>
       </c>
       <c r="V93" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W93" t="n">
-        <v>3.883374558303886</v>
+        <v>-0.5219470404984425</v>
       </c>
     </row>
     <row r="94">
@@ -7532,25 +7532,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D95" t="n">
-        <v>19.54</v>
+        <v>21.14</v>
       </c>
       <c r="E95" t="n">
-        <v>1172.4</v>
+        <v>1268.4</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
         <v>3</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
         <v>5</v>
       </c>
       <c r="M95" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -7586,13 +7586,13 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>22.43907881269191</v>
+        <v>23.26336802270577</v>
       </c>
       <c r="V95" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W95" t="n">
-        <v>3.03080348004094</v>
+        <v>3.352407757805107</v>
       </c>
     </row>
     <row r="96">
@@ -7607,13 +7607,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D96" t="n">
-        <v>28.56</v>
+        <v>28.64</v>
       </c>
       <c r="E96" t="n">
-        <v>1713.6</v>
+        <v>1718.4</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -7661,13 +7661,13 @@
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>27.71388655462184</v>
+        <v>27.63647346368715</v>
       </c>
       <c r="V96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W96" t="n">
-        <v>27.38917366946779</v>
+        <v>27.31266759776536</v>
       </c>
     </row>
     <row r="97">
@@ -7682,67 +7682,67 @@
         </is>
       </c>
       <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1702.8</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
         <v>10</v>
       </c>
-      <c r="D97" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1606.8</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>9</v>
-      </c>
       <c r="H97" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
         <v>4</v>
       </c>
-      <c r="I97" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>3</v>
-      </c>
       <c r="S97" t="n">
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
-        <v>21.07057505601194</v>
+        <v>21.76173361522198</v>
       </c>
       <c r="V97" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="W97" t="n">
-        <v>-0.8068782673637054</v>
+        <v>-0.3509584214235388</v>
       </c>
     </row>
     <row r="98">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>21.22</v>
+        <v>22.82</v>
       </c>
       <c r="E99" t="n">
-        <v>1273.2</v>
+        <v>1369.2</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -7886,13 +7886,13 @@
         <v>3</v>
       </c>
       <c r="U99" t="n">
-        <v>13.57906220546654</v>
+        <v>12.62698071866784</v>
       </c>
       <c r="V99" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="W99" t="n">
-        <v>-29.00046654099906</v>
+        <v>-26.45670026292726</v>
       </c>
     </row>
     <row r="100">
@@ -7982,13 +7982,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>18.78</v>
+        <v>20.38</v>
       </c>
       <c r="E101" t="n">
-        <v>1126.8</v>
+        <v>1222.8</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -8036,13 +8036,13 @@
         <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>26.28122470713525</v>
+        <v>24.21792934249264</v>
       </c>
       <c r="V101" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="W101" t="n">
-        <v>-29.65534611288605</v>
+        <v>-26.75561334641806</v>
       </c>
     </row>
     <row r="102">
@@ -10232,13 +10232,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" t="n">
-        <v>29.22</v>
+        <v>32.1</v>
       </c>
       <c r="E131" t="n">
-        <v>1753.2</v>
+        <v>1926</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -10286,13 +10286,13 @@
         <v>1</v>
       </c>
       <c r="U131" t="n">
-        <v>20.77581108829569</v>
+        <v>18.91181308411215</v>
       </c>
       <c r="V131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W131" t="n">
-        <v>-11.62376454483231</v>
+        <v>-9.087950155763238</v>
       </c>
     </row>
     <row r="132">
@@ -10382,19 +10382,19 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D133" t="n">
-        <v>32.76</v>
+        <v>35.26</v>
       </c>
       <c r="E133" t="n">
-        <v>1965.6</v>
+        <v>2115.6</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H133" t="n">
         <v>5</v>
@@ -10412,13 +10412,13 @@
         <v>2</v>
       </c>
       <c r="M133" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P133" t="n">
         <v>1</v>
@@ -10436,13 +10436,13 @@
         <v>3</v>
       </c>
       <c r="U133" t="n">
-        <v>25.39734432234432</v>
+        <v>25.36917186613726</v>
       </c>
       <c r="V133" t="n">
         <v>-7</v>
       </c>
       <c r="W133" t="n">
-        <v>-20.15550671550671</v>
+        <v>-15.98183210436755</v>
       </c>
     </row>
     <row r="134">
@@ -10457,13 +10457,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="E134" t="n">
-        <v>225</v>
+        <v>238.8</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -10511,13 +10511,13 @@
         <v>1</v>
       </c>
       <c r="U134" t="n">
-        <v>72.26666666666667</v>
+        <v>68.09045226130652</v>
       </c>
       <c r="V134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W134" t="n">
-        <v>27.99061333333334</v>
+        <v>26.37306532663317</v>
       </c>
     </row>
     <row r="135">
@@ -10607,19 +10607,19 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D136" t="n">
-        <v>21.21</v>
+        <v>21.68</v>
       </c>
       <c r="E136" t="n">
-        <v>1272.6</v>
+        <v>1300.8</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -10637,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
@@ -10661,13 +10661,13 @@
         <v>2</v>
       </c>
       <c r="U136" t="n">
-        <v>16.27225836869401</v>
+        <v>18.08738929889299</v>
       </c>
       <c r="V136" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W136" t="n">
-        <v>20.82035832154644</v>
+        <v>12.15721863468634</v>
       </c>
     </row>
     <row r="137">
@@ -10682,13 +10682,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>0.82</v>
+        <v>1.54</v>
       </c>
       <c r="E137" t="n">
-        <v>49.2</v>
+        <v>92.39999999999999</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -10727,10 +10727,10 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" t="n">
         <v>0</v>
@@ -10739,10 +10739,10 @@
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="W137" t="n">
-        <v>-300</v>
+        <v>-112.987012987013</v>
       </c>
     </row>
     <row r="138">
@@ -10757,13 +10757,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D138" t="n">
-        <v>33.8</v>
+        <v>36.45</v>
       </c>
       <c r="E138" t="n">
-        <v>2028</v>
+        <v>2187</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -10796,7 +10796,7 @@
         <v>2</v>
       </c>
       <c r="P138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q138" t="n">
         <v>1</v>
@@ -10811,13 +10811,13 @@
         <v>5</v>
       </c>
       <c r="U138" t="n">
-        <v>18.68065088757396</v>
+        <v>18.81219478737998</v>
       </c>
       <c r="V138" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="W138" t="n">
-        <v>-20.54995857988166</v>
+        <v>-24.42863100137174</v>
       </c>
     </row>
     <row r="139">
@@ -10832,67 +10832,67 @@
         </is>
       </c>
       <c r="C139" t="n">
+        <v>10</v>
+      </c>
+      <c r="D139" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1492.2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>8</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" t="n">
+        <v>4</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="n">
+        <v>12</v>
+      </c>
+      <c r="L139" t="n">
+        <v>6</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
         <v>9</v>
       </c>
-      <c r="D139" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="E139" t="n">
-        <v>1319.4</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
-        <v>6</v>
-      </c>
-      <c r="H139" t="n">
-        <v>2</v>
-      </c>
-      <c r="I139" t="n">
-        <v>3</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K139" t="n">
-        <v>10</v>
-      </c>
-      <c r="L139" t="n">
-        <v>5</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="P139" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>1</v>
-      </c>
-      <c r="R139" t="n">
+      <c r="S139" t="n">
+        <v>2</v>
+      </c>
+      <c r="T139" t="n">
         <v>7</v>
       </c>
-      <c r="S139" t="n">
-        <v>1</v>
-      </c>
-      <c r="T139" t="n">
-        <v>6</v>
-      </c>
       <c r="U139" t="n">
-        <v>29.67422464756708</v>
+        <v>33.07252915158826</v>
       </c>
       <c r="V139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>10.95906775807186</v>
+        <v>11.61693204664255</v>
       </c>
     </row>
     <row r="140">
@@ -10907,13 +10907,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D140" t="n">
-        <v>31.72</v>
+        <v>32.1</v>
       </c>
       <c r="E140" t="n">
-        <v>1903.2</v>
+        <v>1926</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -10961,13 +10961,13 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>34.96411727616645</v>
+        <v>34.55021183800623</v>
       </c>
       <c r="V140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W140" t="n">
-        <v>2.866692938209329</v>
+        <v>1.810426791277256</v>
       </c>
     </row>
     <row r="141">
@@ -11057,28 +11057,28 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D142" t="n">
-        <v>17.94</v>
+        <v>19.64</v>
       </c>
       <c r="E142" t="n">
-        <v>1076.4</v>
+        <v>1178.4</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I142" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
@@ -11111,13 +11111,13 @@
         <v>2</v>
       </c>
       <c r="U142" t="n">
-        <v>35.53841694537346</v>
+        <v>41.67032586558044</v>
       </c>
       <c r="V142" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W142" t="n">
-        <v>37.36367892976588</v>
+        <v>54.46896130346232</v>
       </c>
     </row>
     <row r="143">
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D144" t="n">
-        <v>48.86</v>
+        <v>51.74</v>
       </c>
       <c r="E144" t="n">
-        <v>2931.6</v>
+        <v>3104.4</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H144" t="n">
         <v>4</v>
@@ -11231,19 +11231,19 @@
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P144" t="n">
         <v>3</v>
@@ -11252,22 +11252,22 @@
         <v>2</v>
       </c>
       <c r="R144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T144" t="n">
         <v>3</v>
       </c>
       <c r="U144" t="n">
-        <v>19.51580024559967</v>
+        <v>20.18510243525319</v>
       </c>
       <c r="V144" t="n">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="W144" t="n">
-        <v>-19.43237617683176</v>
+        <v>-19.27694433706996</v>
       </c>
     </row>
     <row r="145">
@@ -11432,22 +11432,22 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D147" t="n">
-        <v>35.66</v>
+        <v>38.54</v>
       </c>
       <c r="E147" t="n">
-        <v>2139.6</v>
+        <v>2312.4</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
         <v>6</v>
       </c>
       <c r="M147" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -11486,13 +11486,13 @@
         <v>3</v>
       </c>
       <c r="U147" t="n">
-        <v>14.45930173864273</v>
+        <v>14.63272184743124</v>
       </c>
       <c r="V147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W147" t="n">
-        <v>14.34755468311833</v>
+        <v>12.0319304618578</v>
       </c>
     </row>
     <row r="148">
@@ -11507,13 +11507,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D148" t="n">
-        <v>60.31</v>
+        <v>61.03</v>
       </c>
       <c r="E148" t="n">
-        <v>3618.6</v>
+        <v>3661.8</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -11531,10 +11531,10 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L148" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M148" t="n">
         <v>0.25</v>
@@ -11561,13 +11561,13 @@
         <v>7</v>
       </c>
       <c r="U148" t="n">
-        <v>35.8922400928536</v>
+        <v>36.50698017368507</v>
       </c>
       <c r="V148" t="n">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="W148" t="n">
-        <v>-15.26348035151716</v>
+        <v>-16.26315746354252</v>
       </c>
     </row>
     <row r="149">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D151" t="n">
-        <v>54.34</v>
+        <v>56.21</v>
       </c>
       <c r="E151" t="n">
-        <v>3260.4</v>
+        <v>3372.6</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -11786,13 +11786,13 @@
         <v>8</v>
       </c>
       <c r="U151" t="n">
-        <v>38.40325542878174</v>
+        <v>37.12565201921366</v>
       </c>
       <c r="V151" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W151" t="n">
-        <v>18.21871733529628</v>
+        <v>16.86508094645081</v>
       </c>
     </row>
     <row r="152">
@@ -11807,22 +11807,22 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D152" t="n">
-        <v>45.81</v>
+        <v>48.69</v>
       </c>
       <c r="E152" t="n">
-        <v>2748.6</v>
+        <v>2921.4</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I152" t="n">
         <v>4</v>
@@ -11831,13 +11831,13 @@
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L152" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M152" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -11852,22 +11852,22 @@
         <v>3</v>
       </c>
       <c r="R152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T152" t="n">
         <v>4</v>
       </c>
       <c r="U152" t="n">
-        <v>31.56930801135123</v>
+        <v>32.87774080920106</v>
       </c>
       <c r="V152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W152" t="n">
-        <v>-9.502054136651386</v>
+        <v>-9.924261655370712</v>
       </c>
     </row>
     <row r="153">
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D153" t="n">
-        <v>9.1</v>
+        <v>11.27</v>
       </c>
       <c r="E153" t="n">
-        <v>546</v>
+        <v>676.2</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" t="n">
         <v>1</v>
@@ -11912,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -11936,13 +11936,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>5.717087912087911</v>
+        <v>8.498021295474709</v>
       </c>
       <c r="V153" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="W153" t="n">
-        <v>-32.21039560439561</v>
+        <v>-33.98752440106477</v>
       </c>
     </row>
     <row r="154">
@@ -11957,13 +11957,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>13.95</v>
+        <v>14.97</v>
       </c>
       <c r="E154" t="n">
-        <v>837</v>
+        <v>898.2</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -12011,13 +12011,13 @@
         <v>3</v>
       </c>
       <c r="U154" t="n">
-        <v>33.96519713261648</v>
+        <v>31.65093520374081</v>
       </c>
       <c r="V154" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="W154" t="n">
-        <v>-78.90904659498207</v>
+        <v>-76.72193720774882</v>
       </c>
     </row>
     <row r="155">
@@ -12032,13 +12032,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" t="n">
-        <v>12.37</v>
+        <v>13.42</v>
       </c>
       <c r="E155" t="n">
-        <v>742.2</v>
+        <v>805.2</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -12068,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P155" t="n">
         <v>2</v>
@@ -12086,13 +12086,13 @@
         <v>1</v>
       </c>
       <c r="U155" t="n">
-        <v>27.16540016168149</v>
+        <v>25.03994038748137</v>
       </c>
       <c r="V155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W155" t="n">
-        <v>-8.298253839935322</v>
+        <v>-11.19801788375558</v>
       </c>
     </row>
     <row r="156">
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D160" t="n">
-        <v>24.96</v>
+        <v>26.56</v>
       </c>
       <c r="E160" t="n">
-        <v>1497.6</v>
+        <v>1593.6</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -12461,13 +12461,13 @@
         <v>7</v>
       </c>
       <c r="U160" t="n">
-        <v>18.39705528846154</v>
+        <v>17.28879894578314</v>
       </c>
       <c r="V160" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="W160" t="n">
-        <v>11.62180689102564</v>
+        <v>10.48314382530121</v>
       </c>
     </row>
     <row r="161">
@@ -12557,28 +12557,28 @@
         </is>
       </c>
       <c r="C162" t="n">
+        <v>11</v>
+      </c>
+      <c r="D162" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1330.2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>16</v>
+      </c>
+      <c r="H162" t="n">
+        <v>9</v>
+      </c>
+      <c r="I162" t="n">
         <v>10</v>
       </c>
-      <c r="D162" t="n">
-        <v>20.57</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1234.2</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>13</v>
-      </c>
-      <c r="H162" t="n">
-        <v>7</v>
-      </c>
-      <c r="I162" t="n">
-        <v>9</v>
-      </c>
       <c r="J162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K162" t="n">
         <v>2</v>
@@ -12587,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.75</v>
       </c>
       <c r="N162" t="n">
         <v>0</v>
@@ -12611,13 +12611,13 @@
         <v>1</v>
       </c>
       <c r="U162" t="n">
-        <v>41.80202722411278</v>
+        <v>43.33404149751917</v>
       </c>
       <c r="V162" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W162" t="n">
-        <v>73.67737967914438</v>
+        <v>67.83471808750564</v>
       </c>
     </row>
     <row r="163">
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D163" t="n">
-        <v>22.68</v>
+        <v>24.28</v>
       </c>
       <c r="E163" t="n">
-        <v>1360.8</v>
+        <v>1456.8</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -12656,10 +12656,10 @@
         <v>3</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
         <v>0.5416666666666666</v>
@@ -12671,28 +12671,28 @@
         <v>4</v>
       </c>
       <c r="P163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q163" t="n">
         <v>1</v>
       </c>
       <c r="R163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T163" t="n">
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>33.40136243386243</v>
+        <v>35.18710461285008</v>
       </c>
       <c r="V163" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="W163" t="n">
-        <v>-11.16052028218695</v>
+        <v>-10.90480230642504</v>
       </c>
     </row>
     <row r="164">
@@ -12782,13 +12782,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D165" t="n">
-        <v>16.4</v>
+        <v>17.98</v>
       </c>
       <c r="E165" t="n">
-        <v>984</v>
+        <v>1078.8</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -12827,22 +12827,22 @@
         <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T165" t="n">
         <v>4</v>
       </c>
       <c r="U165" t="n">
-        <v>27.82990853658537</v>
+        <v>25.38434371523915</v>
       </c>
       <c r="V165" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>-17.14543292682926</v>
+        <v>-16.03157397107897</v>
       </c>
     </row>
     <row r="166">
@@ -12857,13 +12857,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>5.27</v>
+        <v>5.84</v>
       </c>
       <c r="E166" t="n">
-        <v>316.2</v>
+        <v>350.4</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -12911,13 +12911,13 @@
         <v>1</v>
       </c>
       <c r="U166" t="n">
-        <v>56.1585009487666</v>
+        <v>55.55741438356164</v>
       </c>
       <c r="V166" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W166" t="n">
-        <v>-72.38698292220114</v>
+        <v>-69.53630136986303</v>
       </c>
     </row>
     <row r="167">
